--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -8149,11 +8149,11 @@
       <c r="S73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V73" s="10" t="n">
         <v>4</v>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9773,8 +9773,8 @@
       <c r="S89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T89" s="9" t="n">
-        <v>0</v>
+      <c r="T89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U89" s="9" t="n">
         <v>0</v>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q155" s="9" t="n">
         <v>0</v>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17568,14 +17568,14 @@
       <c r="P165" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q165" s="9" t="n">
-        <v>1</v>
+      <c r="Q165" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T165" s="10" t="n">
         <v>1</v>
@@ -17671,7 +17671,7 @@
         </is>
       </c>
       <c r="P166" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q166" s="10" t="n">
         <v>2</v>
@@ -24252,7 +24252,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -24384,7 +24384,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -24945,7 +24945,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,11 @@
       <c r="AB2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2355,7 +2359,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3680,7 +3688,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3987,7 +3999,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4399,7 +4415,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4500,7 +4520,11 @@
       <c r="AB37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4601,7 +4625,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4904,7 +4932,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -5005,7 +5037,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5413,7 +5449,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5821,7 +5861,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6334,7 +6378,11 @@
       <c r="AB55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6435,7 +6483,11 @@
       <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6746,7 +6798,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -7053,7 +7109,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7562,7 +7622,11 @@
       <c r="AB67" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -8176,7 +8240,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8479,7 +8547,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8685,7 +8757,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -9396,7 +9472,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -10006,7 +10086,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -11436,7 +11520,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11537,7 +11625,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -12454,7 +12546,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -12555,7 +12651,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -13484,7 +13584,11 @@
       <c r="AB125" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -14922,7 +15026,11 @@
       <c r="AB139" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC139" s="4" t="inlineStr"/>
+      <c r="AC139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -17919,7 +18027,11 @@
       <c r="AB168" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC168" s="4" t="inlineStr"/>
+      <c r="AC168" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -18751,7 +18863,11 @@
       <c r="AB176" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC176" s="4" t="inlineStr"/>
+      <c r="AC176" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -18852,7 +18968,11 @@
       <c r="AB177" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC177" s="4" t="inlineStr"/>
+      <c r="AC177" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -19264,7 +19384,11 @@
       <c r="AB181" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC181" s="4" t="inlineStr"/>
+      <c r="AC181" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19668,7 +19792,11 @@
       <c r="AB185" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC185" s="4" t="inlineStr"/>
+      <c r="AC185" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -20492,7 +20620,11 @@
       <c r="AB193" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC193" s="4" t="inlineStr"/>
+      <c r="AC193" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -20593,7 +20725,11 @@
       <c r="AB194" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC194" s="4" t="inlineStr"/>
+      <c r="AC194" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -21207,7 +21343,11 @@
       <c r="AB200" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC200" s="4" t="inlineStr"/>
+      <c r="AC200" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -21825,7 +21965,11 @@
       <c r="AB206" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC206" s="4" t="inlineStr"/>
+      <c r="AC206" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -22031,7 +22175,11 @@
       <c r="AB208" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC208" s="4" t="inlineStr"/>
+      <c r="AC208" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -22132,7 +22280,11 @@
       <c r="AB209" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC209" s="4" t="inlineStr"/>
+      <c r="AC209" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -22233,7 +22385,11 @@
       <c r="AB210" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC210" s="4" t="inlineStr"/>
+      <c r="AC210" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -22334,7 +22490,11 @@
       <c r="AB211" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC211" s="4" t="inlineStr"/>
+      <c r="AC211" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -22536,7 +22696,11 @@
       <c r="AB213" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC213" s="4" t="inlineStr"/>
+      <c r="AC213" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -22742,7 +22906,11 @@
       <c r="AB215" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC215" s="4" t="inlineStr"/>
+      <c r="AC215" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -23154,7 +23322,11 @@
       <c r="AB219" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC219" s="4" t="inlineStr"/>
+      <c r="AC219" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -23356,7 +23528,11 @@
       <c r="AB221" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC221" s="4" t="inlineStr"/>
+      <c r="AC221" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
         </is>
       </c>
     </row>
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>6</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5726,8 +5726,8 @@
       <c r="R49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="9" t="n">
-        <v>1</v>
+      <c r="S49" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T49" s="9" t="n">
         <v>0</v>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10489,8 +10489,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="P176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q176" s="9" t="n">
         <v>1</v>
@@ -22455,7 +22455,7 @@
         <v>2</v>
       </c>
       <c r="Q211" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R211" s="9" t="n">
         <v>0</v>
@@ -24263,7 +24263,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -24593,7 +24593,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3784,8 +3784,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3889,8 +3889,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4511,8 +4511,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4604,11 +4604,11 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W38" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W38" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>4</v>
@@ -5279,13 +5279,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5747,8 +5747,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6006,13 +6006,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6054,7 +6054,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>4</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8730,11 +8730,11 @@
       <c r="S78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
+      <c r="T78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V78" s="9" t="n">
         <v>2</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9541,8 +9541,8 @@
       <c r="P86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" s="9" t="n">
-        <v>1</v>
+      <c r="Q86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10691,8 +10691,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10736,13 +10736,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>4</v>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>0</v>
@@ -12537,8 +12537,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13249,8 +13249,8 @@
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="9" t="n">
         <v>3</v>
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13418,17 +13418,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -13462,11 +13462,11 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X124" s="9" t="n">
         <v>0</v>
@@ -13474,8 +13474,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -16086,7 +16086,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16138,11 +16138,11 @@
       <c r="S150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V150" s="9" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q165" s="10" t="n">
         <v>2</v>
@@ -17738,7 +17738,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17790,8 +17790,8 @@
       <c r="S166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T166" s="9" t="n">
-        <v>0</v>
+      <c r="T166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U166" s="9" t="n">
         <v>0</v>
@@ -19552,7 +19552,7 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q183" s="9" t="n">
         <v>0</v>
@@ -19818,7 +19818,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19888,8 +19888,8 @@
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="9" t="n">
-        <v>0</v>
+      <c r="Z186" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA186" s="10" t="n">
         <v>1</v>
@@ -19919,7 +19919,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19989,8 +19989,8 @@
       <c r="Y187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="9" t="n">
-        <v>0</v>
+      <c r="Z187" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA187" s="10" t="n">
         <v>1</v>
@@ -20064,7 +20064,7 @@
         <v>1</v>
       </c>
       <c r="Q188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R188" s="9" t="n">
         <v>0</v>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20689,8 +20689,8 @@
       <c r="P194" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q194" s="9" t="n">
-        <v>1</v>
+      <c r="Q194" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R194" s="9" t="n">
         <v>0</v>
@@ -20971,13 +20971,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -22201,7 +22201,7 @@
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>10</v>
@@ -22242,16 +22242,16 @@
         </is>
       </c>
       <c r="P209" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q209" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S209" s="9" t="n">
-        <v>0</v>
+      <c r="S209" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T209" s="9" t="n">
         <v>0</v>
@@ -24131,7 +24131,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -24164,7 +24164,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -24197,7 +24197,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -24263,7 +24263,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -24494,7 +24494,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -24527,7 +24527,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -24593,7 +24593,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -24824,7 +24824,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -25022,7 +25022,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -25121,7 +25121,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -25253,7 +25253,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -25319,7 +25319,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25418,7 +25418,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -967,17 +967,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M3" s="7" t="n">
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1169,17 +1169,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1476,17 +1476,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2547,8 +2547,8 @@
       <c r="V18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="9" t="n">
-        <v>3</v>
+      <c r="W18" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>5</v>
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2912,17 +2912,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
@@ -2960,7 +2960,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3114,13 +3114,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3623,17 +3623,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3728,17 +3728,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="7" t="n">
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3833,13 +3833,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -3877,8 +3877,8 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>1</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3934,17 +3934,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="7" t="n">
@@ -3978,11 +3978,11 @@
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>3</v>
+      <c r="V32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>4</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4140,17 +4140,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="7" t="n">
@@ -4184,8 +4184,8 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>3</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4245,17 +4245,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4455,17 +4455,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
@@ -4500,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4972,17 +4972,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
@@ -5178,13 +5178,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5323,11 +5323,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>4</v>
@@ -5384,17 +5384,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5691,17 +5691,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5729,14 +5729,14 @@
       <c r="S49" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5901,17 +5901,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
@@ -6006,13 +6006,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6111,13 +6111,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6212,13 +6212,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6313,17 +6313,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="7" t="n">
@@ -6418,17 +6418,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6523,17 +6523,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="7" t="n">
@@ -6628,13 +6628,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -6733,13 +6733,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -6943,17 +6943,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="7" t="n">
@@ -7044,17 +7044,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -7080,7 +7080,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7149,13 +7149,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7250,13 +7250,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7355,13 +7355,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7396,8 +7396,8 @@
       <c r="T65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
+      <c r="U65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V65" s="10" t="n">
         <v>4</v>
@@ -7456,13 +7456,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7557,17 +7557,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7662,13 +7662,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7868,17 +7868,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
@@ -7973,13 +7973,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
@@ -8074,13 +8074,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8175,17 +8175,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="7" t="n">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>1</v>
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8526,8 +8526,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8898,13 +8898,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8999,13 +8999,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -9100,13 +9100,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="10" t="n">
         <v>2</v>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9306,13 +9306,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -9407,13 +9407,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>1</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9512,13 +9512,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9714,13 +9714,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9815,17 +9815,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="7" t="n">
@@ -9860,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9920,13 +9920,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10021,13 +10021,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10126,13 +10126,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
@@ -10227,13 +10227,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -10328,13 +10328,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10534,13 +10534,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10578,8 +10578,8 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>2</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10736,17 +10736,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="7" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10946,13 +10946,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
@@ -11047,13 +11047,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -11253,13 +11253,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
@@ -11354,13 +11354,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -11455,13 +11455,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11560,13 +11560,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11665,13 +11665,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11766,13 +11766,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11867,13 +11867,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11968,13 +11968,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -12069,13 +12069,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
@@ -12170,13 +12170,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>5</v>
@@ -12275,17 +12275,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="7" t="n">
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -12481,17 +12481,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="7" t="n">
@@ -12526,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12630,11 +12630,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>4</v>
@@ -12691,13 +12691,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12796,17 +12796,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="7" t="n">
@@ -12901,13 +12901,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -13006,13 +13006,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13107,13 +13107,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L121" s="8" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13208,13 +13208,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13252,8 +13252,8 @@
       <c r="U122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>3</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13465,8 +13465,8 @@
       <c r="V124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>1</v>
+      <c r="W124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X124" s="9" t="n">
         <v>0</v>
@@ -13519,17 +13519,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -13624,17 +13624,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -13711,7 +13711,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13725,13 +13725,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13763,14 +13763,14 @@
       <c r="S127" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13917,7 +13917,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13931,13 +13931,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13975,8 +13975,8 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>2</v>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -14032,17 +14032,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -14137,17 +14137,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="7" t="n">
@@ -14242,13 +14242,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
@@ -14347,13 +14347,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -14452,13 +14452,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -14553,13 +14553,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -14654,17 +14654,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="7" t="n">
@@ -14755,13 +14755,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L137" s="8" t="inlineStr">
         <is>
@@ -14856,17 +14856,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14961,13 +14961,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -15066,13 +15066,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
@@ -15167,13 +15167,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>4</v>
       </c>
       <c r="W141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>6</v>
@@ -15272,13 +15272,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15377,17 +15377,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="7" t="n">
@@ -15482,13 +15482,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L144" s="8" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15583,13 +15583,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -15688,13 +15688,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
@@ -15789,17 +15789,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="7" t="n">
@@ -15894,13 +15894,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15995,17 +15995,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="7" t="n">
@@ -16039,8 +16039,8 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="9" t="n">
-        <v>3</v>
+      <c r="V149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -16100,13 +16100,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
@@ -16201,17 +16201,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16302,13 +16302,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16451,11 +16451,11 @@
       <c r="U153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W153" s="9" t="n">
-        <v>0</v>
+      <c r="V153" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W153" s="10" t="n">
+        <v>17</v>
       </c>
       <c r="X153" s="10" t="n">
         <v>4</v>
@@ -16512,17 +16512,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -16617,17 +16617,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="7" t="n">
@@ -16647,7 +16647,7 @@
         <v>3</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
@@ -16665,7 +16665,7 @@
         <v>4</v>
       </c>
       <c r="W155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X155" s="10" t="n">
         <v>6</v>
@@ -16722,13 +16722,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L156" s="8" t="inlineStr">
         <is>
@@ -16924,17 +16924,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="7" t="n">
@@ -17029,13 +17029,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
@@ -17231,17 +17231,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L161" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M161" s="7" t="n">
@@ -17336,17 +17336,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L162" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="7" t="n">
@@ -17437,17 +17437,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L163" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="7" t="n">
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
@@ -17647,17 +17647,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M165" s="7" t="n">
@@ -17752,13 +17752,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17857,17 +17857,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="7" t="n">
@@ -17901,8 +17901,8 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>2</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
@@ -17962,13 +17962,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -18172,13 +18172,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -18273,13 +18273,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18378,17 +18378,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L172" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M172" s="7" t="n">
@@ -18483,17 +18483,17 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L173" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M173" s="7" t="n">
@@ -18528,7 +18528,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -18588,17 +18588,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="7" t="n">
@@ -18693,17 +18693,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L175" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="7" t="n">
@@ -18784,7 +18784,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18798,13 +18798,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18842,8 +18842,8 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>2</v>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L178" s="8" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -19109,17 +19109,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="7" t="n">
@@ -19214,17 +19214,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L180" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="7" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19424,13 +19424,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L182" s="8" t="inlineStr">
         <is>
@@ -19525,13 +19525,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L183" s="8" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>1</v>
       </c>
       <c r="V183" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W183" s="9" t="n">
         <v>0</v>
@@ -19626,13 +19626,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L184" s="8" t="inlineStr">
         <is>
@@ -19727,17 +19727,17 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L185" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L185" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M185" s="7" t="n">
@@ -19832,13 +19832,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L186" s="8" t="inlineStr">
         <is>
@@ -19933,13 +19933,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L187" s="8" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -20034,13 +20034,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L188" s="8" t="inlineStr">
         <is>
@@ -20063,14 +20063,14 @@
       <c r="P188" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" s="9" t="n">
-        <v>1</v>
+      <c r="Q188" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R188" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T188" s="9" t="n">
         <v>0</v>
@@ -20139,13 +20139,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" s="8" t="inlineStr">
         <is>
@@ -20244,13 +20244,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -20349,13 +20349,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="L191" s="8" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>1</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
         <v>0</v>
       </c>
       <c r="V192" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W192" s="9" t="n">
         <v>0</v>
@@ -20555,13 +20555,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
@@ -20660,17 +20660,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L194" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M194" s="7" t="n">
@@ -20765,13 +20765,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L195" s="8" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>4</v>
       </c>
       <c r="W196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X196" s="10" t="n">
         <v>4</v>
@@ -20971,13 +20971,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
@@ -21072,17 +21072,17 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L198" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M198" s="7" t="n">
@@ -21173,17 +21173,17 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L199" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M199" s="7" t="n">
@@ -21218,7 +21218,7 @@
         <v>0</v>
       </c>
       <c r="V199" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W199" s="9" t="n">
         <v>0</v>
@@ -21278,17 +21278,17 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L200" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M200" s="7" t="n">
@@ -21383,13 +21383,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L201" s="8" t="inlineStr">
         <is>
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L202" s="8" t="inlineStr">
         <is>
@@ -21585,13 +21585,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>10</v>
@@ -21690,13 +21690,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
@@ -21734,8 +21734,8 @@
       <c r="U204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V204" s="9" t="n">
-        <v>3</v>
+      <c r="V204" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W204" s="9" t="n">
         <v>0</v>
@@ -21795,13 +21795,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>4</v>
       </c>
       <c r="W206" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X206" s="10" t="n">
         <v>7</v>
@@ -22005,17 +22005,17 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L207" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M207" s="7" t="n">
@@ -22110,13 +22110,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -22215,13 +22215,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>0</v>
       </c>
       <c r="V209" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W209" s="9" t="n">
         <v>0</v>
@@ -22306,7 +22306,7 @@
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>10</v>
@@ -22320,13 +22320,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         </is>
       </c>
       <c r="P210" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q210" s="9" t="n">
         <v>1</v>
@@ -22367,8 +22367,8 @@
       <c r="V210" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W210" s="9" t="n">
-        <v>2</v>
+      <c r="W210" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X210" s="10" t="n">
         <v>5</v>
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>10</v>
@@ -22425,13 +22425,13 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
@@ -22469,8 +22469,8 @@
       <c r="U211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V211" s="9" t="n">
-        <v>3</v>
+      <c r="V211" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W211" s="9" t="n">
         <v>0</v>
@@ -22631,13 +22631,13 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J213" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>0</v>
       </c>
       <c r="V213" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W213" s="9" t="n">
         <v>0</v>
@@ -22736,17 +22736,17 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J214" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L214" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M214" s="7" t="n">
@@ -22781,7 +22781,7 @@
         <v>0</v>
       </c>
       <c r="V214" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W214" s="9" t="n">
         <v>0</v>
@@ -22841,13 +22841,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>0</v>
       </c>
       <c r="V215" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W215" s="9" t="n">
         <v>0</v>
@@ -22946,17 +22946,17 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L216" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L216" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M216" s="7" t="n">
@@ -23047,13 +23047,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
@@ -23152,13 +23152,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="V218" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W218" s="9" t="n">
         <v>0</v>
@@ -23257,13 +23257,13 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>1</v>
       </c>
       <c r="V219" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W219" s="9" t="n">
         <v>0</v>
@@ -23348,7 +23348,7 @@
         </is>
       </c>
       <c r="E220" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>10</v>
@@ -23362,17 +23362,17 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K220" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L220" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M220" s="7" t="n">
@@ -23409,8 +23409,8 @@
       <c r="V220" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W220" s="9" t="n">
-        <v>0</v>
+      <c r="W220" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X220" s="10" t="n">
         <v>6</v>
@@ -23463,17 +23463,17 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K221" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L221" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M221" s="7" t="n">
@@ -23508,7 +23508,7 @@
         <v>0</v>
       </c>
       <c r="V221" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W221" s="9" t="n">
         <v>0</v>
@@ -23568,17 +23568,17 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K222" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L222" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M222" s="7" t="n">
@@ -23601,7 +23601,7 @@
         <v>2</v>
       </c>
       <c r="R222" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S222" s="9" t="n">
         <v>0</v>
@@ -23613,7 +23613,7 @@
         <v>0</v>
       </c>
       <c r="V222" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W222" s="9" t="n">
         <v>0</v>
@@ -23659,7 +23659,7 @@
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>10</v>
@@ -23673,13 +23673,13 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K223" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
@@ -23717,8 +23717,8 @@
       <c r="U223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V223" s="9" t="n">
-        <v>3</v>
+      <c r="V223" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W223" s="9" t="n">
         <v>0</v>
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K224" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L224" s="8" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -23981,7 +23981,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -24032,7 +24032,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -24080,7 +24080,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -24131,7 +24131,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -24146,7 +24146,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -24164,7 +24164,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -24179,7 +24179,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -24230,7 +24230,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -24245,7 +24245,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -24263,7 +24263,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -24278,7 +24278,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -24311,7 +24311,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -24344,7 +24344,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -24377,7 +24377,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -24395,22 +24395,22 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -24443,7 +24443,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -24461,7 +24461,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -24575,7 +24575,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -24593,7 +24593,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -24641,7 +24641,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -24740,7 +24740,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -24758,7 +24758,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -24791,7 +24791,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -24824,7 +24824,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -24857,7 +24857,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -24872,7 +24872,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -24938,7 +24938,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -24971,7 +24971,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -25004,7 +25004,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -25022,7 +25022,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -25037,7 +25037,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -25070,7 +25070,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -25121,7 +25121,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -25136,7 +25136,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -25169,7 +25169,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -25187,7 +25187,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -25202,7 +25202,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -25235,7 +25235,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -25253,7 +25253,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -25268,7 +25268,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25367,7 +25367,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -25385,7 +25385,7 @@
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -25400,7 +25400,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -25418,7 +25418,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -25466,7 +25466,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -25484,7 +25484,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -25499,7 +25499,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -25517,7 +25517,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -25532,7 +25532,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3934,17 +3934,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M32" s="7" t="n">
@@ -3982,7 +3982,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>4</v>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6313,13 +6313,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6357,8 +6357,8 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>3</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8523,14 +8523,14 @@
       <c r="T76" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U76" s="9" t="n">
-        <v>0</v>
+      <c r="U76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>7</v>
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" s="10" t="n">
         <v>2</v>
@@ -10021,13 +10021,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
@@ -13624,13 +13624,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>4</v>
@@ -14374,7 +14374,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>1</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15894,13 +15894,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
@@ -15923,8 +15923,8 @@
       <c r="P148" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q148" s="9" t="n">
-        <v>1</v>
+      <c r="Q148" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -15932,14 +15932,14 @@
       <c r="S148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T148" s="9" t="n">
-        <v>0</v>
+      <c r="T148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15981,7 +15981,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -16033,8 +16033,8 @@
       <c r="S149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T149" s="9" t="n">
-        <v>0</v>
+      <c r="T149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U149" s="9" t="n">
         <v>0</v>
@@ -16201,17 +16201,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16249,7 +16249,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>4</v>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16652,8 +16652,8 @@
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S155" s="9" t="n">
-        <v>1</v>
+      <c r="S155" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T155" s="10" t="n">
         <v>1</v>
@@ -17029,13 +17029,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -17130,13 +17130,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>4</v>
@@ -17738,7 +17738,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17752,13 +17752,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -17793,11 +17793,11 @@
       <c r="T166" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U166" s="9" t="n">
-        <v>0</v>
+      <c r="U166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -17948,7 +17948,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17962,13 +17962,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -18006,8 +18006,8 @@
       <c r="U168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V168" s="9" t="n">
-        <v>3</v>
+      <c r="V168" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -18067,13 +18067,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>4</v>
       </c>
       <c r="W169" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X169" s="10" t="n">
         <v>4</v>
@@ -18588,13 +18588,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L174" s="8" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -18950,8 +18950,8 @@
       <c r="V177" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W177" s="9" t="n">
-        <v>2</v>
+      <c r="W177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X177" s="10" t="n">
         <v>4</v>
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L178" s="8" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>1</v>
       </c>
       <c r="Q182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" s="9" t="n">
         <v>0</v>
@@ -19727,13 +19727,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="L185" s="8" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         </is>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q186" s="9" t="n">
         <v>0</v>
@@ -20660,17 +20660,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L194" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M194" s="7" t="n">
@@ -20705,7 +20705,7 @@
         <v>1</v>
       </c>
       <c r="V194" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W194" s="9" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="S196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T196" s="10" t="n">
         <v>1</v>
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -21009,8 +21009,8 @@
       <c r="S197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T197" s="9" t="n">
-        <v>0</v>
+      <c r="T197" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U197" s="9" t="n">
         <v>0</v>
@@ -21383,13 +21383,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L201" s="8" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -24146,7 +24146,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -24296,7 +24296,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -24461,7 +24461,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -24989,7 +24989,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -25022,7 +25022,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -25037,7 +25037,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -25055,13 +25055,13 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25121,7 +25121,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -25187,7 +25187,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -25319,7 +25319,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25334,7 +25334,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">

--- a/docs/d/118/inyear.xlsx
+++ b/docs/d/118/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4289,8 +4289,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4607,8 +4607,8 @@
       <c r="V38" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>2</v>
+      <c r="W38" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>4</v>
@@ -6242,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6970,19 +6970,19 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8210,8 +8210,8 @@
       <c r="R73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="9" t="n">
-        <v>1</v>
+      <c r="S73" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T73" s="10" t="n">
         <v>1</v>
@@ -9142,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="U82" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" s="10" t="n">
         <v>4</v>
@@ -9205,13 +9205,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9407,13 +9407,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9451,11 +9451,11 @@
       <c r="U85" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>3</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>5</v>
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11665,13 +11665,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11709,8 +11709,8 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>3</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -12481,13 +12481,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -13235,7 +13235,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -13830,13 +13830,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -14539,7 +14539,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14553,13 +14553,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -14597,11 +14597,11 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>3</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>4</v>
@@ -14684,7 +14684,7 @@
         <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -16100,13 +16100,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>1</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16646,11 +16646,11 @@
       <c r="P155" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q155" s="9" t="n">
-        <v>1</v>
+      <c r="Q155" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S155" s="10" t="n">
         <v>2</v>
@@ -17322,7 +17322,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17336,17 +17336,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L162" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M162" s="7" t="n">
@@ -17380,8 +17380,8 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>3</v>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17647,17 +17647,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L165" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M165" s="7" t="n">
@@ -17688,14 +17688,14 @@
       <c r="T165" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U165" s="9" t="n">
-        <v>0</v>
+      <c r="U165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V165" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W165" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>4</v>
@@ -17788,7 +17788,7 @@
         <v>0</v>
       </c>
       <c r="S166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166" s="10" t="n">
         <v>1</v>
@@ -17962,13 +17962,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>4</v>
       </c>
       <c r="W168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X168" s="10" t="n">
         <v>4</v>
@@ -18378,13 +18378,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L172" s="8" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18693,17 +18693,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L175" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M175" s="7" t="n">
@@ -18740,8 +18740,8 @@
       <c r="V175" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W175" s="9" t="n">
-        <v>2</v>
+      <c r="W175" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>4</v>
@@ -21278,13 +21278,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L200" s="8" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>0</v>
       </c>
       <c r="V200" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W200" s="9" t="n">
         <v>0</v>
@@ -21717,7 +21717,7 @@
         </is>
       </c>
       <c r="P204" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q204" s="9" t="n">
         <v>0</v>
@@ -22035,7 +22035,7 @@
         <v>1</v>
       </c>
       <c r="Q207" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R207" s="9" t="n">
         <v>0</v>
@@ -22306,7 +22306,7 @@
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>10</v>
@@ -22358,8 +22358,8 @@
       <c r="S210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T210" s="9" t="n">
-        <v>0</v>
+      <c r="T210" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U210" s="9" t="n">
         <v>0</v>
@@ -22827,7 +22827,7 @@
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>10</v>
@@ -22841,13 +22841,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -22885,8 +22885,8 @@
       <c r="U215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V215" s="9" t="n">
-        <v>3</v>
+      <c r="V215" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W215" s="9" t="n">
         <v>0</v>
@@ -23659,7 +23659,7 @@
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>10</v>
@@ -23702,8 +23702,8 @@
       <c r="P223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" s="9" t="n">
-        <v>0</v>
+      <c r="Q223" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R223" s="9" t="n">
         <v>0</v>
@@ -24164,7 +24164,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -24197,7 +24197,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -24362,7 +24362,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -24428,13 +24428,13 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -24527,13 +24527,13 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -24692,7 +24692,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -24890,7 +24890,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -25055,7 +25055,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -25088,7 +25088,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -25121,13 +25121,13 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25136,7 +25136,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -25154,7 +25154,7 @@
         <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -25169,7 +25169,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -25418,7 +25418,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -25451,7 +25451,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -25517,7 +25517,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
